--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_Maciek\Uczelnia\praca\przedmioty\Integrated Energy Resource Planning\2025_2026\winter\ELAND_01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aghedupl.sharepoint.com/sites/Prywatny238/Shared Documents/General/Wymiana_Danych/ELAND_01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3125DA2-228A-4F56-9458-5B702E3A969B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{6509FE2B-FEAB-40C2-B885-50F7D9B47643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5699028A-D0B4-4A3C-A258-E7CBDA231D86}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="18696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="18816" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Region-Time Slices" sheetId="2" r:id="rId1"/>
@@ -1284,7 +1284,7 @@
     </row>
     <row r="5" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
-        <v>2025</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="7" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -1317,10 +1317,14 @@
       </c>
     </row>
     <row r="12" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="13"/>
+      <c r="B12" s="13">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="2:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="8"/>
+      <c r="B13" s="8">
+        <v>5</v>
+      </c>
     </row>
     <row r="14" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14"/>
@@ -1525,7 +1529,7 @@
         <v>33</v>
       </c>
       <c r="D6" s="26">
-        <v>2025</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1545,7 +1549,8 @@
         <v>80</v>
       </c>
       <c r="D8" s="29">
-        <v>1</v>
+        <f>1/96</f>
+        <v>1.0416666666666666E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1981,6 +1986,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100765A2D8ABDD1064B8560F0E0020228D7" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="faba48c57225b8cf4893994d76bae982">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="154c1c0f-2c06-4f37-a5b1-faba3524bf7f" xmlns:ns3="0be4b9af-ad17-4489-a21e-b8b210aeb5f9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="653a6a65a0f1497e1436c43ea8aacb76" ns2:_="" ns3:_="">
     <xsd:import namespace="154c1c0f-2c06-4f37-a5b1-faba3524bf7f"/>
@@ -2175,15 +2189,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06DF0508-E134-4C36-AFE9-9AAFDD53DF25}">
   <ds:schemaRefs>
@@ -2196,6 +2201,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC507C37-6D94-49C9-9631-28E3A5FDD97F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C22B888-B004-4DDB-A401-1DC505E37364}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2212,12 +2225,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC507C37-6D94-49C9-9631-28E3A5FDD97F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>